--- a/output/pdf_financials_xlsx/SGY.xlsx
+++ b/output/pdf_financials_xlsx/SGY.xlsx
@@ -2425,10 +2425,10 @@
         <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>7.594</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>18.654</v>
       </c>
     </row>
     <row r="35">
@@ -2541,10 +2541,10 @@
         <v>0</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>7.594</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>18.654</v>
       </c>
     </row>
     <row r="37">
@@ -3237,10 +3237,10 @@
         <v>10.059</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>17.287</v>
+        <v>9.693</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>29.229</v>
+        <v>10.575</v>
       </c>
     </row>
     <row r="49">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21155,7 +21155,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -59542,7 +59542,7 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">

--- a/output/pdf_financials_xlsx/SGY.xlsx
+++ b/output/pdf_financials_xlsx/SGY.xlsx
@@ -7514,13 +7514,13 @@
         <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>56.405</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>0</v>
+        <v>1.406</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>302.07</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
@@ -34817,7 +34817,11 @@
           <t>Issue of common shares, net of issue costs</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SGY.xlsx
+++ b/output/pdf_financials_xlsx/SGY.xlsx
@@ -1358,7 +1358,7 @@
         <v>18.252</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>4.053</v>
+        <v>5.545</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>22.126</v>
@@ -2264,7 +2264,7 @@
         <v>-25.52905797608224</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-29.07669129779755</v>
+        <v>-39.780472056819</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-40.00867945681066</v>
@@ -6290,7 +6290,7 @@
         <v>7.697575</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-2.112</v>
+        <v>-2.112138</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-7.695</v>
@@ -24823,7 +24823,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -25787,7 +25791,11 @@
           <t>Deferred income tax expense (recovery) (note 15)</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -29852,7 +29860,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -33213,7 +33225,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -34512,7 +34528,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -35643,7 +35663,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -38487,7 +38511,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E306" s="5" t="n">
         <v>7.697575</v>
       </c>
@@ -47696,7 +47724,11 @@
           <t>Deferred income tax recovery (note 16)</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -49149,7 +49181,11 @@
           <t>Deferred income tax recovery (note 14)</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -50297,7 +50333,11 @@
           <t>Deferred income tax recovery (note 15)</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -55118,7 +55158,11 @@
           <t>Deferred income tax recovery (note 16)</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
